--- a/DEBUG_JML_LOC.xlsx
+++ b/DEBUG_JML_LOC.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T77"/>
+  <dimension ref="A1:T47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,7 +520,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3320070506479</v>
+        <v>3320052818159</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -534,12 +534,12 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2104051301</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>35930-182</t>
+          <t>35930-286</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -551,7 +551,11 @@
       <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:43:34</t>
+        </is>
+      </c>
       <c r="J2" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -559,12 +563,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>D21025775801</t>
+          <t>D2108862101</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -574,12 +578,12 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-06-04 10:38:28</t>
+          <t>2026-08-13 09:27:34</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -597,7 +601,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -608,7 +612,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3320097491460</v>
+        <v>3320060812954</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -617,17 +621,17 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2104051301</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-360</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -639,7 +643,11 @@
       <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-10 18:48:47</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -647,12 +655,12 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>D21020403501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML INT)ANA RAQUEL MALAQUIAS-NOVA ERA </t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -662,12 +670,12 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-06-04 15:54:02</t>
+          <t>2026-08-13 10:39:30</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML INT)ANA RAQUEL MALAQUIAS-NOVA ERA </t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -676,7 +684,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -685,7 +693,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -696,11 +704,11 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3320093496251</v>
+        <v>6081026603855</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>In Transit</t>
+          <t>Delivery</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -710,12 +718,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>35931-201</t>
+          <t>35930-022</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -727,7 +735,11 @@
       <c r="H4" t="n">
         <v>2</v>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-11 15:11:08</t>
+        </is>
+      </c>
       <c r="J4" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -737,12 +749,12 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Offloading</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-06-04 05:58:22</t>
+          <t>2026-08-13 14:57:35</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -761,18 +773,18 @@
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>Descarregado</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>3320003501099</v>
+        <v>3320080804111</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -791,7 +803,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>35930-133</t>
+          <t>35931-085</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -809,29 +821,21 @@
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>D21025775801</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Out For Delivery</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-06-04 10:36:06</t>
+          <t>2026-08-13 14:56:55</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t xml:space="preserve">CESAR JUNIO DA SILVA </t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -840,27 +844,23 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>EM ROTA</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3320037508592</v>
+        <v>6081026352986</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -869,17 +869,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-338</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -891,7 +891,11 @@
       <c r="H6" t="n">
         <v>2</v>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-11 07:35:38</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -899,12 +903,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -914,12 +918,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:21</t>
+          <t>2026-08-13 10:39:12</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -937,7 +941,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -948,7 +952,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>3320023501439</v>
+        <v>3320048829382</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -967,7 +971,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>35931-073</t>
+          <t>35930-331</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -987,12 +991,12 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>D2108865601</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -1002,12 +1006,12 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-06-04 08:57:01</t>
+          <t>2026-08-13 10:40:11</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>GUSTAVO VIEIRA LEANDRO</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1025,7 +1029,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1036,7 +1040,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>6053126306460</v>
+        <v>6081026607467</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1045,17 +1049,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>C2103940801</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-159</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1069,7 +1073,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-06-02 17:14:42</t>
+          <t>2026-08-11 07:20:34</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1079,12 +1083,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1094,12 +1098,12 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-06-04 08:44:20</t>
+          <t>2026-08-13 10:23:11</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1108,7 +1112,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -1117,7 +1121,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1128,7 +1132,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3320086504381</v>
+        <v>6081026642434</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1142,12 +1146,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103941301</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35930-129</t>
+          <t>35931-159</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1159,7 +1163,11 @@
       <c r="H9" t="n">
         <v>2</v>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-10 11:04:06</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -1167,12 +1175,12 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>D21025775801</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1182,12 +1190,12 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2026-06-04 10:36:12</t>
+          <t>2026-08-13 10:22:38</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1205,7 +1213,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
@@ -1216,7 +1224,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>6060126389113</v>
+        <v>3320082807985</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1225,17 +1233,17 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>C2103941301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-169</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1249,7 +1257,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2026-06-02 15:16:13</t>
+          <t>2026-08-10 16:55:00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1259,12 +1267,12 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1274,12 +1282,12 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:07</t>
+          <t>2026-08-13 10:22:36</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1288,7 +1296,7 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10" t="inlineStr">
         <is>
@@ -1297,7 +1305,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -1308,7 +1316,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>3320077506614</v>
+        <v>3320092817587</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1327,7 +1335,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>35930-045</t>
+          <t>35930-332</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1339,27 +1347,39 @@
       <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-10 14:05:57</t>
+        </is>
+      </c>
       <c r="J11" t="inlineStr">
         <is>
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>D21020045101</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Arrive</t>
+          <t>Out For Delivery</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2026-06-04 06:06:43</t>
+          <t>2026-08-13 10:39:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t xml:space="preserve">CESAR JUNIO DA SILVA </t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1370,21 +1390,25 @@
       <c r="Q11" t="n">
         <v>0</v>
       </c>
-      <c r="R11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
+        </is>
+      </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>Recebido no DS</t>
+          <t>EM ROTA</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3320030507877</v>
+        <v>3320047829716</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1403,7 +1427,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>35930-295</t>
+          <t>35931-000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1423,12 +1447,12 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>D21011865601</t>
+          <t>D2108864201</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML LOC) MARC RODRIGO DA COSTA SILVA </t>
+          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1438,12 +1462,12 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2026-06-04 09:41:52</t>
+          <t>2026-08-13 19:11:38</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML LOC) MARC RODRIGO DA COSTA SILVA </t>
+          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1461,7 +1485,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -1472,7 +1496,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3320000503551</v>
+        <v>6081026835270</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1481,17 +1505,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-191</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1505,7 +1529,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-06-01 16:30:26</t>
+          <t>2026-08-11 07:12:06</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1515,12 +1539,12 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D21034183101</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t xml:space="preserve">(JML LOC)TIAGO SALES MENDES </t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1530,12 +1554,12 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2026-06-04 07:43:17</t>
+          <t>2026-08-13 10:04:53</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t xml:space="preserve">(JML LOC)TIAGO SALES MENDES </t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1544,7 +1568,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
@@ -1564,7 +1588,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3320019507425</v>
+        <v>3320058818976</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1573,7 +1597,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>SAO DOMINGOS DO PRATA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1583,7 +1607,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>35995-000</t>
+          <t>35930-249</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1597,7 +1621,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2026-06-01 15:01:46</t>
+          <t>2026-08-10 16:09:53</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1607,12 +1631,12 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>D21021404601</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML INT) YURI ANTONIO - PRATA </t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1622,12 +1646,12 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2026-06-04 08:23:11</t>
+          <t>2026-08-13 10:38:51</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>Matheus Augusto</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1645,7 +1669,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
@@ -1656,7 +1680,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3320087498491</v>
+        <v>3320015815342</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -1665,17 +1689,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2104051301</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-362</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1687,7 +1711,11 @@
       <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-10 15:34:27</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -1695,12 +1723,12 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1710,12 +1738,12 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2026-06-04 08:15:20</t>
+          <t>2026-08-13 10:38:48</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -1733,7 +1761,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
@@ -1744,7 +1772,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3320089509212</v>
+        <v>3320051819570</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1763,7 +1791,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>35931-075</t>
+          <t>35931-027</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1781,29 +1809,21 @@
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>D21011846401</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WITALO MUNIZ MOREIRA </t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Out For Delivery</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2026-06-04 11:17:23</t>
+          <t>2026-08-13 14:57:49</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML LOC) WITALO MUNIZ MOREIRA </t>
+          <t xml:space="preserve">CESAR JUNIO DA SILVA </t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -1812,27 +1832,23 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>EM ROTA</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>6060126259694</v>
+        <v>6080926697046</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1841,7 +1857,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1851,7 +1867,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-331</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1865,7 +1881,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2026-06-01 15:49:22</t>
+          <t>2026-08-10 16:34:23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1875,12 +1891,12 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1890,12 +1906,12 @@
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>2026-06-04 07:45:20</t>
+          <t>2026-08-13 10:39:01</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -1913,7 +1929,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
@@ -1924,7 +1940,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6060226328107</v>
+        <v>3320010815585</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1933,17 +1949,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>C2103733101</t>
+          <t>C2104051301</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-043</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1957,7 +1973,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2026-06-01 17:21:23</t>
+          <t>2026-08-10 15:58:52</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1967,12 +1983,12 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D2108862101</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1982,12 +1998,12 @@
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2026-06-04 08:15:25</t>
+          <t>2026-08-13 08:50:53</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -1996,7 +2012,7 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18" t="inlineStr">
         <is>
@@ -2005,7 +2021,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
@@ -2016,7 +2032,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>3320075509720</v>
+        <v>6080926638057</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2030,12 +2046,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>35930-129</t>
+          <t>35930-362</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2047,7 +2063,11 @@
       <c r="H19" t="n">
         <v>2</v>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-11 07:22:04</t>
+        </is>
+      </c>
       <c r="J19" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -2055,12 +2075,12 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>D21025775801</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -2070,12 +2090,12 @@
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2026-06-04 10:38:03</t>
+          <t>2026-08-13 10:39:25</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2084,7 +2104,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -2093,7 +2113,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
@@ -2104,7 +2124,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>3320013514583</v>
+        <v>3320025826712</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2113,7 +2133,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2123,7 +2143,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-073</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2135,11 +2155,7 @@
       <c r="H20" t="n">
         <v>2</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2026-06-02 16:17:41</t>
-        </is>
-      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -2147,12 +2163,12 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D2108865601</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2162,12 +2178,12 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2026-06-04 08:44:23</t>
+          <t>2026-08-13 10:07:37</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>Mateus Francisco</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2185,7 +2201,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
@@ -2196,7 +2212,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>3320054492721</v>
+        <v>3320086814398</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2215,7 +2231,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>35931-193</t>
+          <t>35931-208</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2227,35 +2243,31 @@
       <c r="H21" t="n">
         <v>2</v>
       </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:34:36</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr">
         <is>
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>D2108864201</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Out For Delivery</t>
+          <t>Arrive</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2026-06-04 09:57:17</t>
+          <t>2026-08-13 02:33:17</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
+          <t>Rayner</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2264,27 +2276,23 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>1</v>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>EM ROTA</t>
+          <t>Recebido no DS</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3320030504728</v>
+        <v>3320069817423</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -2293,7 +2301,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2303,7 +2311,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-073</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2323,12 +2331,12 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D2108865601</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -2338,12 +2346,12 @@
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:42</t>
+          <t>2026-08-13 10:07:09</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>Mateus Francisco</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2361,7 +2369,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
@@ -2372,7 +2380,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>3320060501133</v>
+        <v>3320091827122</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2386,12 +2394,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>C2104051301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35930-191</t>
+          <t>35931-236</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2405,7 +2413,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-06-01 16:08:58</t>
+          <t>2026-08-11 18:46:53</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2415,12 +2423,12 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>D21033548401</t>
+          <t>D2108861101</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>(JML LOC) ROGER CARLOS BRAGA</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2430,12 +2438,12 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2026-06-04 09:27:17</t>
+          <t>2026-08-13 10:22:14</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>(JML LOC) ROGER CARLOS BRAGA</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2453,7 +2461,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
@@ -2464,7 +2472,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>3320000519920</v>
+        <v>3320084804831</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2483,7 +2491,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>35931-490</t>
+          <t>35930-367</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2495,11 +2503,7 @@
       <c r="H24" t="n">
         <v>2</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2026-06-02 12:49:09</t>
-        </is>
-      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -2522,12 +2526,12 @@
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>2026-06-04 09:50:23</t>
+          <t>2026-08-13 10:40:15</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2536,7 +2540,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -2545,7 +2549,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
@@ -2556,7 +2560,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6060126820106</v>
+        <v>3320021822410</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2570,12 +2574,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35930-463</t>
+          <t>35931-147</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2589,7 +2593,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-06-02 05:09:47</t>
+          <t>2026-08-10 17:58:37</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2599,12 +2603,12 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>D21025775801</t>
+          <t>D2108864101</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) RANDLER JUNIOR PINHEIRO ARAUJO</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -2614,12 +2618,12 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2026-06-04 10:36:08</t>
+          <t>2026-08-13 10:00:34</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) RANDLER JUNIOR PINHEIRO ARAUJO</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -2637,7 +2641,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
@@ -2648,7 +2652,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3320054497099</v>
+        <v>3320015810678</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2657,17 +2661,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>C2104051301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-362</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2681,7 +2685,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-06-01 11:47:51</t>
+          <t>2026-08-10 16:37:01</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2691,12 +2695,12 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2706,12 +2710,12 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>2026-06-04 08:42:52</t>
+          <t>2026-08-13 10:38:38</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -2729,7 +2733,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
@@ -2740,7 +2744,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6053026656166</v>
+        <v>3320015828801</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -2754,12 +2758,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>35930-301</t>
+          <t>35931-333</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2771,31 +2775,35 @@
       <c r="H27" t="n">
         <v>2</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2026-06-02 09:03:20</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>D21033548401</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Inventory Scan</t>
+          <t>Out For Delivery</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>2026-06-04 11:30:29</t>
+          <t>2026-08-13 10:22:56</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>YAGO FÉLIX TEIXEIRA</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -2804,23 +2812,27 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
+        </is>
+      </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>Inventory Scan</t>
+          <t>EM ROTA</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6060126209008</v>
+        <v>6080926668901</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -2834,12 +2846,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>C2103941301</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>35931-020</t>
+          <t>35930-610</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2853,7 +2865,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2026-06-01 14:46:26</t>
+          <t>2026-08-12 16:01:26</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2863,12 +2875,12 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>D2108865601</t>
+          <t>D21025775801</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
+          <t>(JML LOC) THALLES GOMES VIANA</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2878,12 +2890,12 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>2026-06-04 14:31:33</t>
+          <t>2026-08-13 10:14:17</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
+          <t>GUSTAVO VIEIRA LEANDRO</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -2901,7 +2913,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
@@ -2912,7 +2924,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>3320006516064</v>
+        <v>3320056818580</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -2921,17 +2933,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>C2104051301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-248</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2945,7 +2957,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>2026-06-02 14:07:14</t>
+          <t>2026-08-11 19:10:46</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2955,12 +2967,12 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21025775801</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) THALLES GOMES VIANA</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2970,12 +2982,12 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:48</t>
+          <t>2026-08-13 10:14:00</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) THALLES GOMES VIANA</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -2984,7 +2996,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -2993,7 +3005,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
@@ -3004,7 +3016,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6060226608549</v>
+        <v>3320091806440</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3013,17 +3025,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-249</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3035,11 +3047,7 @@
       <c r="H30" t="n">
         <v>2</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2026-06-02 06:52:51</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -3047,12 +3055,12 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -3062,12 +3070,12 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>2026-06-04 08:42:45</t>
+          <t>2026-08-13 10:39:06</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3085,7 +3093,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
@@ -3096,7 +3104,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>3320082498460</v>
+        <v>3320014818656</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3105,7 +3113,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3115,7 +3123,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35930-040</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3135,12 +3143,12 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D2108862101</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3150,12 +3158,12 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>2026-06-04 08:15:30</t>
+          <t>2026-08-13 08:51:44</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3164,7 +3172,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -3173,7 +3181,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
@@ -3184,7 +3192,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6053126404379</v>
+        <v>6081026619837</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3193,17 +3201,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2103941301</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-337</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -3217,7 +3225,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2026-06-02 15:30:38</t>
+          <t>2026-08-10 14:25:51</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3227,12 +3235,12 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3242,12 +3250,12 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:54</t>
+          <t>2026-08-13 10:38:45</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3265,7 +3273,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
@@ -3276,7 +3284,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>3320090490389</v>
+        <v>3320013816651</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3285,7 +3293,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3295,7 +3303,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-215</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3309,7 +3317,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-06-01 16:08:25</t>
+          <t>2026-08-10 17:05:56</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3319,12 +3327,12 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3334,12 +3342,12 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:59</t>
+          <t>2026-08-13 10:22:54</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3348,7 +3356,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -3357,7 +3365,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
@@ -3368,7 +3376,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>6060226340789</v>
+        <v>3320067829262</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3377,17 +3385,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35931-267</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -3401,7 +3409,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>2026-06-02 16:47:09</t>
+          <t>2026-08-11 15:44:13</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3411,12 +3419,12 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D2108864101</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) RANDLER JUNIOR PINHEIRO ARAUJO</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3426,12 +3434,12 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>2026-06-04 08:15:32</t>
+          <t>2026-08-13 10:00:56</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>Gabriel</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
@@ -3449,7 +3457,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
@@ -3460,7 +3468,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3320058494983</v>
+        <v>3320028820769</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3479,7 +3487,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>35930-167</t>
+          <t>35930-338</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -3499,12 +3507,12 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>D21010352501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>(JML LOC) LUCAS DE SOUZA SILVA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -3514,12 +3522,12 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2026-06-04 09:58:10</t>
+          <t>2026-08-13 10:38:50</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>(JML LOC) LUCAS DE SOUZA SILVA</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
@@ -3528,7 +3536,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -3537,7 +3545,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
@@ -3548,7 +3556,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>3320000518481</v>
+        <v>3320034790781</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3557,7 +3565,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3567,7 +3575,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-554</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -3587,12 +3595,12 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21025775801</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) THALLES GOMES VIANA</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3602,12 +3610,12 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>2026-06-04 08:44:02</t>
+          <t>2026-08-13 10:15:04</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>GUSTAVO VIEIRA LEANDRO</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -3625,7 +3633,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
@@ -3636,7 +3644,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>3320073500493</v>
+        <v>3320037829864</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -3645,7 +3653,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3655,7 +3663,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-085</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3667,35 +3675,31 @@
       <c r="H37" t="n">
         <v>2</v>
       </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2026-08-10 16:16:20</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr">
         <is>
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Out For Delivery</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2026-06-04 08:44:11</t>
+          <t>2026-08-13 14:56:56</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t xml:space="preserve">CESAR JUNIO DA SILVA </t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -3706,25 +3710,21 @@
       <c r="Q37" t="n">
         <v>0</v>
       </c>
-      <c r="R37" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
+      <c r="R37" t="inlineStr"/>
       <c r="S37" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>EM ROTA</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>3320053492740</v>
+        <v>6081026100022</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -3738,12 +3738,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>35932-156</t>
+          <t>35931-159</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -3755,7 +3755,11 @@
       <c r="H38" t="n">
         <v>2</v>
       </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2026-08-11 12:36:00</t>
+        </is>
+      </c>
       <c r="J38" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -3763,12 +3767,12 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>D21025775801</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -3778,12 +3782,12 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>2026-06-04 10:38:37</t>
+          <t>2026-08-13 10:23:09</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>(JML LOC) THALLES GOMES VIANA</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -3801,7 +3805,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
@@ -3812,7 +3816,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>3320008507407</v>
+        <v>3320031804052</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -3821,17 +3825,17 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>C2104051301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-208</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -3845,7 +3849,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>2026-06-01 15:41:04</t>
+          <t>2026-08-10 16:32:21</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3855,12 +3859,12 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -3870,12 +3874,12 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>2026-06-04 08:44:25</t>
+          <t>2026-08-13 10:22:30</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -3884,7 +3888,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -3893,7 +3897,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
@@ -3904,7 +3908,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>3320028502249</v>
+        <v>3320007818457</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -3923,7 +3927,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>35931-209</t>
+          <t>35930-331</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3937,7 +3941,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>2026-06-02 14:45:05</t>
+          <t>2026-08-10 15:05:33</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3947,12 +3951,12 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>D21033548401</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -3962,12 +3966,12 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>2026-06-04 09:27:54</t>
+          <t>2026-08-13 10:38:46</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -3976,7 +3980,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -3985,7 +3989,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
@@ -3996,7 +4000,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>6052926655842</v>
+        <v>3320087806012</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4010,12 +4014,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>35931-210</t>
+          <t>35931-103</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4027,11 +4031,7 @@
       <c r="H41" t="n">
         <v>2</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-06-02 16:04:25</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -4039,12 +4039,12 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>D21033548401</t>
+          <t>D21028187301</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>(JML LOC)MARLON NILSON DE SOUZA</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -4054,12 +4054,12 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>2026-06-04 09:27:39</t>
+          <t>2026-08-13 12:04:43</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
+          <t>(JML LOC)MARLON NILSON DE SOUZA</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4077,7 +4077,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
@@ -4088,7 +4088,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>3320071490951</v>
+        <v>3320010822081</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4097,17 +4097,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2104051301</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-332</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4119,7 +4119,11 @@
       <c r="H42" t="n">
         <v>2</v>
       </c>
-      <c r="I42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2026-08-10 09:57:43</t>
+        </is>
+      </c>
       <c r="J42" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -4127,12 +4131,12 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4142,12 +4146,12 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:15</t>
+          <t>2026-08-13 10:40:08</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -4165,7 +4169,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
@@ -4176,7 +4180,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6053126606117</v>
+        <v>3320031814562</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4190,12 +4194,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>C2103718801</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>35931-209</t>
+          <t>35931-168</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4207,11 +4211,7 @@
       <c r="H43" t="n">
         <v>2</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:59:39</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -4234,7 +4234,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>2026-06-04 09:27:28</t>
+          <t>2026-08-13 10:23:06</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
@@ -4268,7 +4268,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>3320083493438</v>
+        <v>3320015829969</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4277,17 +4277,17 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>C2104051301</t>
+          <t>C2104008501</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-191</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>2026-06-01 16:12:50</t>
+          <t>2026-08-10 12:29:07</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4309,29 +4309,21 @@
           <t>Not Closed</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Out For Delivery</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:36</t>
+          <t>2026-08-13 14:58:46</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t xml:space="preserve">CESAR JUNIO DA SILVA </t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -4342,25 +4334,21 @@
       <c r="Q44" t="n">
         <v>0</v>
       </c>
-      <c r="R44" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
+      <c r="R44" t="inlineStr"/>
       <c r="S44" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>EM ROTA</t>
+          <t>Inventory Scan</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>3320017509567</v>
+        <v>3320060820516</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4369,7 +4357,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NOVA ERA</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4379,7 +4367,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>35920-000</t>
+          <t>35931-073</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4399,12 +4387,12 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>D2108867201</t>
+          <t>D2108865601</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
+          <t>(JML LOC) LUIGI DUARTE DE SOUZA</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -4414,12 +4402,12 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>2026-06-04 08:15:23</t>
+          <t>2026-08-13 10:07:57</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
+          <t>Mateus Francisco</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -4437,7 +4425,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
@@ -4448,7 +4436,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>3320095498698</v>
+        <v>3320083807789</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4457,7 +4445,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4467,7 +4455,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35931-160</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4479,7 +4467,11 @@
       <c r="H46" t="n">
         <v>2</v>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>2026-08-10 10:01:51</t>
+        </is>
+      </c>
       <c r="J46" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -4487,12 +4479,12 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21033548401</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -4502,12 +4494,12 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>2026-06-04 08:42:39</t>
+          <t>2026-08-13 10:23:04</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>(JML LOC) DANIEL SANTOS MOURA</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -4516,7 +4508,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -4525,7 +4517,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
@@ -4536,7 +4528,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>3320001508440</v>
+        <v>6081026384494</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -4545,17 +4537,17 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>DIONISIO</t>
+          <t>JOAO MONLEVADE</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>C2104008501</t>
+          <t>C2103718801</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35984-000</t>
+          <t>35930-362</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4567,7 +4559,11 @@
       <c r="H47" t="n">
         <v>2</v>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2026-08-11 16:34:44</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr">
         <is>
           <t>Not Closed</t>
@@ -4575,12 +4571,12 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>D21032378501</t>
+          <t>D21020045101</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
+          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4590,12 +4586,12 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>2026-06-04 08:43:45</t>
+          <t>2026-08-13 10:38:35</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Luan Vitor</t>
+          <t>EDESIO VALERIANO GOMES</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -4613,2662 +4609,10 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>RJ1-E09-359</t>
+          <t>MG1-JML-359</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>3320008514556</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>NOVA ERA</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>35920-000</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="n">
-        <v>2</v>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>2026-06-02 17:30:01</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>D2108867201</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>2026-06-04 07:43:59</t>
-        </is>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
-        </is>
-      </c>
-      <c r="P48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S48" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T48" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>3320056506927</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>35930-008</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="n">
-        <v>2</v>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>2026-06-04 11:32:57</t>
-        </is>
-      </c>
-      <c r="O49" t="inlineStr">
-        <is>
-          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
-        </is>
-      </c>
-      <c r="P49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q49" t="n">
-        <v>1</v>
-      </c>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T49" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>3320063495480</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>35930-079</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="n">
-        <v>2</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:45:12</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>2026-06-04 11:31:34</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>YAGO FÉLIX TEIXEIRA</t>
-        </is>
-      </c>
-      <c r="P50" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T50" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>3320011513603</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>C2104051301</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="n">
-        <v>2</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:38:14</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:42:36</t>
-        </is>
-      </c>
-      <c r="O51" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S51" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T51" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>3320067509983</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>35930-356</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="n">
-        <v>2</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-06-01 17:37:35</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>D2108864201</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:57:03</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q52" t="n">
-        <v>1</v>
-      </c>
-      <c r="R52" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>3320092505775</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="n">
-        <v>2</v>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:43:17</t>
-        </is>
-      </c>
-      <c r="O53" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P53" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S53" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T53" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>6060126321688</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>C2103941301</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="n">
-        <v>2</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-06-02 10:18:49</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:44:26</t>
-        </is>
-      </c>
-      <c r="O54" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T54" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>3320075506515</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>35931-210</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="n">
-        <v>2</v>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>D21033548401</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:27:30</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q55" t="n">
-        <v>1</v>
-      </c>
-      <c r="R55" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>3320086508863</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>35931-200</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="n">
-        <v>2</v>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>D2108864201</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:57:16</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q56" t="n">
-        <v>1</v>
-      </c>
-      <c r="R56" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S56" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T56" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>3320087498614</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="n">
-        <v>2</v>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:43:03</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
-      <c r="R57" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S57" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T57" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>3320024505009</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="n">
-        <v>2</v>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:43:11</t>
-        </is>
-      </c>
-      <c r="O58" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P58" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
-      <c r="R58" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S58" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T58" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>3320091495085</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>SAO DOMINGOS DO PRATA</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>35995-000</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="n">
-        <v>2</v>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>D21021404601</t>
-        </is>
-      </c>
-      <c r="L59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT) YURI ANTONIO - PRATA </t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:12:59</t>
-        </is>
-      </c>
-      <c r="O59" t="inlineStr">
-        <is>
-          <t>Matheus Augusto</t>
-        </is>
-      </c>
-      <c r="P59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
-      <c r="R59" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S59" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T59" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>3320075501031</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="n">
-        <v>2</v>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:42:59</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>3320068496435</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>NOVA ERA</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>35920-000</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="n">
-        <v>2</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:39:31</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>D21020403501</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT)ANA RAQUEL MALAQUIAS-NOVA ERA </t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr">
-        <is>
-          <t>2026-06-04 16:10:50</t>
-        </is>
-      </c>
-      <c r="O61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT)ANA RAQUEL MALAQUIAS-NOVA ERA </t>
-        </is>
-      </c>
-      <c r="P61" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q61" t="n">
-        <v>1</v>
-      </c>
-      <c r="R61" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S61" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T61" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>6060126428071</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>C2103941301</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>35931-188</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="n">
-        <v>2</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2026-06-02 17:22:50</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>D2108864201</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:57:14</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML LOC) WASHINGTON TULIO ALMEIDA </t>
-        </is>
-      </c>
-      <c r="P62" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q62" t="n">
-        <v>1</v>
-      </c>
-      <c r="R62" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S62" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T62" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>3320010517946</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>SAO DOMINGOS DO PRATA</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>35995-000</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="n">
-        <v>2</v>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>D21021404601</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT) YURI ANTONIO - PRATA </t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:12:13</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>Matheus Augusto</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
-      <c r="R63" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S63" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T63" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>3320009510628</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>35931-210</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="n">
-        <v>2</v>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>D21033548401</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:27:58</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q64" t="n">
-        <v>1</v>
-      </c>
-      <c r="R64" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S64" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T64" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>3320097503844</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="n">
-        <v>2</v>
-      </c>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:44:17</t>
-        </is>
-      </c>
-      <c r="O65" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S65" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3320045509035</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>SAO DOMINGOS DO PRATA</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>35995-000</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="n">
-        <v>2</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>2026-06-01 15:39:08</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>D21021404601</t>
-        </is>
-      </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT) YURI ANTONIO - PRATA </t>
-        </is>
-      </c>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:12:38</t>
-        </is>
-      </c>
-      <c r="O66" t="inlineStr">
-        <is>
-          <t>Matheus Augusto</t>
-        </is>
-      </c>
-      <c r="P66" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q66" t="n">
-        <v>0</v>
-      </c>
-      <c r="R66" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S66" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T66" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>6053026270361</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>C2103941301</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>35930-175</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="n">
-        <v>2</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2026-06-01 12:35:58</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>Arrive</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>2026-06-04 06:51:38</t>
-        </is>
-      </c>
-      <c r="O67" t="inlineStr">
-        <is>
-          <t>EDESIO VALERIANO GOMES</t>
-        </is>
-      </c>
-      <c r="P67" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
-      <c r="R67" t="inlineStr"/>
-      <c r="S67" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
-        <is>
-          <t>Recebido no DS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3320071509047</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>NOVA ERA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>C2104051301</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>35920-000</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="n">
-        <v>2</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2026-06-02 15:58:33</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>D2108867201</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>(JML INT)BRUNO FELIPE - NOVA ERA</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
-        <is>
-          <t>2026-06-04 07:43:53</t>
-        </is>
-      </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>RIAN PABLO JUNIO DOS SANTOS SILVA</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
-      <c r="R68" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S68" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T68" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>3320070494960</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>35931-186</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>D21033548401</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:27:32</t>
-        </is>
-      </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>1</v>
-      </c>
-      <c r="R69" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S69" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>3320030509222</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>35930-385</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="n">
-        <v>2</v>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>D21020045101</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:50:18</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q70" t="n">
-        <v>1</v>
-      </c>
-      <c r="R70" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S70" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T70" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>6053026284983</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>DIONISIO</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>C2103718801</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>35984-000</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="n">
-        <v>2</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:22:51</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>D21032378501</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>(JML INT) IVAN NELIS XAVIER - DIONISIO</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:43:51</t>
-        </is>
-      </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>Luan Vitor</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
-      <c r="R71" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S71" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T71" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3320078494407</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>35930-001</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="n">
-        <v>2</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>2026-06-01 16:15:07</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>D2108862101</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:46:29</t>
-        </is>
-      </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>(JML LOC) RENNER DIEGO DE CARVALHO</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q72" t="n">
-        <v>1</v>
-      </c>
-      <c r="R72" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S72" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T72" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>6053126663681</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>C2103718801</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>35931-209</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="n">
-        <v>2</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:22:27</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>D21033548401</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:27:50</t>
-        </is>
-      </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q73" t="n">
-        <v>1</v>
-      </c>
-      <c r="R73" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S73" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T73" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>3320061507105</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>35930-381</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="n">
-        <v>2</v>
-      </c>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>D21020045101</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:51:28</t>
-        </is>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>(JML LOC) JOÃO PAULO BICALHO MARTINS</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q74" t="n">
-        <v>1</v>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S74" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>6053126440561</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>C2103718801</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>35930-060</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="n">
-        <v>2</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:23:08</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>2026-06-04 11:29:52</t>
-        </is>
-      </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>YAGO FÉLIX TEIXEIRA</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
-      <c r="R75" t="inlineStr"/>
-      <c r="S75" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T75" t="inlineStr">
-        <is>
-          <t>Inventory Scan</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>6060226682812</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>SAO DOMINGOS DO PRATA</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>C2103718801</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>35995-000</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="n">
-        <v>2</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2026-06-02 14:56:45</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>D21021404601</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(JML INT) YURI ANTONIO - PRATA </t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>2026-06-04 08:11:35</t>
-        </is>
-      </c>
-      <c r="O76" t="inlineStr">
-        <is>
-          <t>Matheus Augusto</t>
-        </is>
-      </c>
-      <c r="P76" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S76" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T76" t="inlineStr">
-        <is>
-          <t>EM ROTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3320014504657</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Delivery</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>JOAO MONLEVADE</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>C2104008501</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>35931-209</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>****</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="n">
-        <v>2</v>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>Not Closed</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>D21033548401</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Out For Delivery</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>2026-06-04 09:27:51</t>
-        </is>
-      </c>
-      <c r="O77" t="inlineStr">
-        <is>
-          <t>(JML LOC) DANIEL SANTOS MOURA</t>
-        </is>
-      </c>
-      <c r="P77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q77" t="n">
-        <v>1</v>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>PORTO GUIMARAES POLO JOAO MONLEVADE LTDA</t>
-        </is>
-      </c>
-      <c r="S77" t="inlineStr">
-        <is>
-          <t>RJ1-E09-359</t>
-        </is>
-      </c>
-      <c r="T77" t="inlineStr">
         <is>
           <t>EM ROTA</t>
         </is>
